--- a/sheets/대금율보/검수/티끌같은 세상 이슬같은 세상.xlsx
+++ b/sheets/대금율보/검수/티끌같은 세상 이슬같은 세상.xlsx
@@ -4824,8 +4824,7 @@
       <c r="I10" s="27"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K10" s="28" t="inlineStr">
@@ -5365,8 +5364,7 @@
       <c r="I18" s="27"/>
       <c r="J18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="K18" s="28" t="inlineStr">

--- a/sheets/대금율보/검수/티끌같은 세상 이슬같은 세상.xlsx
+++ b/sheets/대금율보/검수/티끌같은 세상 이슬같은 세상.xlsx
@@ -4279,30 +4279,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="79.8" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="79.8" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23"/>
       <c r="C4" s="25"/>
@@ -4474,7 +4474,7 @@
       <c r="R4" s="23"/>
       <c r="S4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="79.8" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="23"/>
       <c r="C5" s="25"/>
@@ -4513,7 +4513,7 @@
       <c r="R5" s="23"/>
       <c r="S5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="79.8" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="S6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="79.8" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="79.8" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="23"/>
       <c r="C8" s="25"/>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="79.8" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
       <c r="R9" s="23"/>
       <c r="S9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="79.8" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="S10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="79.8" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="79.8" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="23"/>
       <c r="C12" s="25"/>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="S12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="79.8" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="23"/>
       <c r="C13" s="25"/>
@@ -5070,7 +5070,7 @@
       <c r="R13" s="23"/>
       <c r="S13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="79.8" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
       <c r="R14" s="23"/>
       <c r="S14" s="27"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="79.8" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="23"/>
       <c r="C15" s="24"/>
@@ -5205,7 +5205,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="79.8" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="23"/>
       <c r="C16" s="25"/>
@@ -5285,7 +5285,7 @@
       <c r="R16" s="23"/>
       <c r="S16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="79.8" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="23"/>
       <c r="C17" s="25"/>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="79.8" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="23"/>
       <c r="C18" s="27"/>
@@ -5411,6 +5411,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>